--- a/r4-core-154-polish-use-of-abbreviations-and-technical-terms-in-profiles/StructureDefinition-at-core-location.xlsx
+++ b/r4-core-154-polish-use-of-abbreviations-and-technical-terms-in-profiles/StructureDefinition-at-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T13:14:26+00:00</t>
+    <t>2026-10-14T13:25:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -491,7 +491,7 @@
     <t>Krankenanstaltennummer (KA-Nr)</t>
   </si>
   <si>
-    <t>The hospital identification number (Krankenanstaltennummer, KA-Nr) of the hospital site in the more fine-grained 6-character format ('K' + 3 digits + '.' + 1 digit, e.g. 'K460.1'), assigned by the Federal Ministry of Health (Bundesministerium für Gesundheit). The 4-character KA-Nr remains an identifier on the Organization resource only. The first 4 characters of the Location KA-Nr SHALL match the Organization KA-Nr.</t>
+    <t>The hospital identification number (Krankenanstaltennummer, KA-Nr) of the hospital site in the more fine-grained 6-character format ('K' + 3 digits + '.' + 1 digit, e.g. 'K460.1'), assigned by the Federal Ministry of Health (Österreichisches Bundesministerium für Gesundheit). The 4-character KA-Nr remains an identifier on the Organization resource only. The first 4 characters of the Location KA-Nr SHALL match the Organization KA-Nr.</t>
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
@@ -642,7 +642,7 @@
     <t>Location.identifier.value</t>
   </si>
   <si>
-    <t>Krankenanstaltennummer (hospital identification number) in the more fine-grained 6-character format, used to represent a hospital site. The 4-character hospital identification number remains an identifier on the Organization resource only. The first 4 characters of the Location KANR SHALL match the Organization KANR.“</t>
+    <t>Krankenanstaltennummer (hospital identification number) in the more fine-grained 6-character format, used to represent a hospital site. The 4-character hospital identification number remains an identifier on the Organization resource only. The first 4 characters of the Location KA-Nr SHALL match the Organization KA-Nr.</t>
   </si>
   <si>
     <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>

--- a/r4-core-154-polish-use-of-abbreviations-and-technical-terms-in-profiles/StructureDefinition-at-core-location.xlsx
+++ b/r4-core-154-polish-use-of-abbreviations-and-technical-terms-in-profiles/StructureDefinition-at-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T13:25:21+00:00</t>
+    <t>2026-10-19T13:57:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3351,10 +3351,10 @@
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S17" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="S17" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="T17" t="s" s="2">
         <v>197</v>
@@ -4319,10 +4319,10 @@
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S26" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="S26" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="T26" t="s" s="2">
         <v>21</v>

--- a/r4-core-154-polish-use-of-abbreviations-and-technical-terms-in-profiles/StructureDefinition-at-core-location.xlsx
+++ b/r4-core-154-polish-use-of-abbreviations-and-technical-terms-in-profiles/StructureDefinition-at-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T13:57:06+00:00</t>
+    <t>2026-10-19T15:00:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-154-polish-use-of-abbreviations-and-technical-terms-in-profiles/StructureDefinition-at-core-location.xlsx
+++ b/r4-core-154-polish-use-of-abbreviations-and-technical-terms-in-profiles/StructureDefinition-at-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T15:00:46+00:00</t>
+    <t>2026-10-20T05:56:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
